--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ237"/>
+  <dimension ref="A1:AZ238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23384,10 +23384,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>6864741</v>
+        <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>106229</v>
+        <v>110098</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23395,16 +23395,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -23412,35 +23412,24 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Ruvallen, 450 m NO, Hjd</t>
+          <t>Ruvallen Mässlingen, Hjd</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>394415</v>
+        <v>394495</v>
       </c>
       <c r="R218" t="n">
-        <v>6952036</v>
+        <v>6952089</v>
       </c>
       <c r="S218" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -23464,12 +23453,22 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2013-07-09</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2013-07-09</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23478,35 +23477,31 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Anders Nordlund</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Crister Albinsson, Stina Eriksson</t>
+          <t>Anders Nordlund</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6864741</t>
+          <t>https://artportalen.se/Sighting/136920799</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>60675814</v>
+        <v>6864741</v>
       </c>
       <c r="B219" t="n">
         <v>106229</v>
@@ -23534,20 +23529,35 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Ruvallen - hällmålningningarna, Hjd</t>
+          <t>Ruvallen, 450 m NO, Hjd</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>395139</v>
+        <v>394415</v>
       </c>
       <c r="R219" t="n">
-        <v>6951888</v>
+        <v>6952036</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23571,12 +23581,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2016-07-08</t>
+          <t>2013-07-09</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2016-07-08</t>
+          <t>2013-07-09</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23590,30 +23600,30 @@
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Anita Stridvall</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Crister Albinsson, Stina Eriksson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60675814</t>
+          <t>https://artportalen.se/Sighting/6864741</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>86287159</v>
+        <v>60675814</v>
       </c>
       <c r="B220" t="n">
         <v>106229</v>
@@ -23642,20 +23652,16 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Ruvallen Ö, Hjd</t>
+          <t>Ruvallen - hällmålningningarna, Hjd</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>394332</v>
+        <v>395139</v>
       </c>
       <c r="R220" t="n">
-        <v>6951780</v>
+        <v>6951888</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23682,12 +23688,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2016-07-08</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2016-07-08</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23698,31 +23704,36 @@
       </c>
       <c r="AG220" t="b">
         <v>0</v>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>Fjällbjörkskog</t>
+        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anita Stridvall</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander, Richard Vestin, Nicklas Johansson</t>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86287159</t>
+          <t>https://artportalen.se/Sighting/60675814</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>86287049</v>
+        <v>86287159</v>
       </c>
       <c r="B221" t="n">
-        <v>99140</v>
+        <v>106229</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23730,37 +23741,41 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>Ruvallen Ö, Hjd</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>394311</v>
+        <v>394332</v>
       </c>
       <c r="R221" t="n">
-        <v>6951681</v>
+        <v>6951780</v>
       </c>
       <c r="S221" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -23804,68 +23819,65 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen</t>
+          <t>Bo karlstens, Håkan Thenander, Richard Vestin, Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86287049</t>
+          <t>https://artportalen.se/Sighting/86287159</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>82022118</v>
+        <v>86287049</v>
       </c>
       <c r="B222" t="n">
-        <v>81332</v>
+        <v>99140</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229436</v>
+        <v>221952</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>393930</v>
+        <v>394311</v>
       </c>
       <c r="R222" t="n">
-        <v>6951430</v>
+        <v>6951681</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -23889,12 +23901,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2020-02-02</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2020-02-02</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23903,73 +23915,74 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82022118</t>
+          <t>https://artportalen.se/Sighting/86287049</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>86274479</v>
+        <v>82022118</v>
       </c>
       <c r="B223" t="n">
-        <v>80392</v>
+        <v>81332</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>229497</v>
+        <v>229436</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>394780</v>
+        <v>393930</v>
       </c>
       <c r="R223" t="n">
-        <v>6951685</v>
+        <v>6951430</v>
       </c>
       <c r="S223" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -23993,27 +24006,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2020-02-02</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Noterad. På sälg.</t>
+          <t>2020-02-02</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24022,30 +24020,31 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
+      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Nicklas Johansson, Richard Vestin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86274479</t>
+          <t>https://artportalen.se/Sighting/82022118</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>86286590</v>
+        <v>86274479</v>
       </c>
       <c r="B224" t="n">
         <v>80392</v>
@@ -24074,19 +24073,20 @@
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>394968</v>
+        <v>394780</v>
       </c>
       <c r="R224" t="n">
-        <v>6951677</v>
+        <v>6951685</v>
       </c>
       <c r="S224" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -24113,9 +24113,24 @@
           <t>2020-06-15</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Noterad. På sälg.</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24130,24 +24145,24 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Julian Klein, Bjarne Tutturen, Barbara Kühn</t>
+          <t>Nicklas Johansson, Richard Vestin</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86286590</t>
+          <t>https://artportalen.se/Sighting/86274479</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>86286591</v>
+        <v>86286590</v>
       </c>
       <c r="B225" t="n">
         <v>80392</v>
@@ -24182,10 +24197,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>394670</v>
+        <v>394968</v>
       </c>
       <c r="R225" t="n">
-        <v>6951658</v>
+        <v>6951677</v>
       </c>
       <c r="S225" t="n">
         <v>15</v>
@@ -24243,13 +24258,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86286591</t>
+          <t>https://artportalen.se/Sighting/86286590</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>86287668</v>
+        <v>86286591</v>
       </c>
       <c r="B226" t="n">
         <v>80392</v>
@@ -24278,22 +24293,19 @@
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Ruvallen Ö, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>394339</v>
+        <v>394670</v>
       </c>
       <c r="R226" t="n">
-        <v>6951805</v>
+        <v>6951658</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -24323,11 +24335,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2020-06-15</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Sälglåga 70m</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24342,24 +24349,24 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander, Richard Vestin, Nicklas Johansson</t>
+          <t>Julian Klein, Bjarne Tutturen, Barbara Kühn</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86287668</t>
+          <t>https://artportalen.se/Sighting/86286591</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>86288693</v>
+        <v>86287668</v>
       </c>
       <c r="B227" t="n">
         <v>80392</v>
@@ -24397,10 +24404,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>394394</v>
+        <v>394339</v>
       </c>
       <c r="R227" t="n">
-        <v>6951763</v>
+        <v>6951805</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24437,7 +24444,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Sälglåga 70-80 cm</t>
+          <t>Sälglåga 70m</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24463,13 +24470,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86288693</t>
+          <t>https://artportalen.se/Sighting/86287668</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>86375196</v>
+        <v>86288693</v>
       </c>
       <c r="B228" t="n">
         <v>80392</v>
@@ -24498,16 +24505,19 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Ruvallen öst, Hjd</t>
+          <t>Ruvallen Ö, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>395040</v>
+        <v>394394</v>
       </c>
       <c r="R228" t="n">
-        <v>6951728</v>
+        <v>6951763</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24542,6 +24552,11 @@
           <t>2020-06-15</t>
         </is>
       </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Sälglåga 70-80 cm</t>
+        </is>
+      </c>
       <c r="AD228" t="b">
         <v>0</v>
       </c>
@@ -24554,24 +24569,24 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Richard Vestin, Niklas Johansson, Bo karlstens, Håkan Thenander, Julian Klein, Barbara Kühn</t>
+          <t>Bo karlstens, Håkan Thenander, Richard Vestin, Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86375196</t>
+          <t>https://artportalen.se/Sighting/86288693</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>86386157</v>
+        <v>86375196</v>
       </c>
       <c r="B229" t="n">
         <v>80392</v>
@@ -24600,19 +24615,16 @@
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Ruvallen Öst, Hjd</t>
+          <t>Ruvallen öst, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>395151</v>
+        <v>395040</v>
       </c>
       <c r="R229" t="n">
-        <v>6951745</v>
+        <v>6951728</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24653,7 +24665,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -24665,22 +24676,22 @@
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Richard Vestin, Niklas Johansson, Bo karlstens, Håkan Thenander, Barbara Kühn, Julian Klein</t>
+          <t>Bjarne Tutturen, Richard Vestin, Niklas Johansson, Bo karlstens, Håkan Thenander, Julian Klein, Barbara Kühn</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86386157</t>
+          <t>https://artportalen.se/Sighting/86375196</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>86274510</v>
+        <v>86386157</v>
       </c>
       <c r="B230" t="n">
-        <v>80398</v>
+        <v>80392</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24688,38 +24699,40 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>229748</v>
+        <v>229497</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Ruvallen Öst, Hjd</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>394787</v>
+        <v>395151</v>
       </c>
       <c r="R230" t="n">
-        <v>6951675</v>
+        <v>6951745</v>
       </c>
       <c r="S230" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -24746,56 +24759,42 @@
           <t>2020-06-15</t>
         </is>
       </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>2020-06-15</t>
         </is>
       </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Noterad, på sälg.</t>
-        </is>
-      </c>
       <c r="AD230" t="b">
         <v>0</v>
       </c>
       <c r="AE230" t="b">
         <v>0</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Nicklas Johansson, Richard Vestin</t>
+          <t>Bjarne Tutturen, Richard Vestin, Niklas Johansson, Bo karlstens, Håkan Thenander, Barbara Kühn, Julian Klein</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86274510</t>
+          <t>https://artportalen.se/Sighting/86386157</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>86286594</v>
+        <v>86274510</v>
       </c>
       <c r="B231" t="n">
         <v>80398</v>
@@ -24824,19 +24823,20 @@
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Ruvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>395120</v>
+        <v>394787</v>
       </c>
       <c r="R231" t="n">
-        <v>6951862</v>
+        <v>6951675</v>
       </c>
       <c r="S231" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -24863,9 +24863,24 @@
           <t>2020-06-15</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Noterad, på sälg.</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24880,24 +24895,24 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Julian Klein, Bjarne Tutturen, Barbara Kühn</t>
+          <t>Nicklas Johansson, Richard Vestin</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86286594</t>
+          <t>https://artportalen.se/Sighting/86274510</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>86287061</v>
+        <v>86286594</v>
       </c>
       <c r="B232" t="n">
         <v>80398</v>
@@ -24932,10 +24947,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>394475</v>
+        <v>395120</v>
       </c>
       <c r="R232" t="n">
-        <v>6951692</v>
+        <v>6951862</v>
       </c>
       <c r="S232" t="n">
         <v>15</v>
@@ -24993,13 +25008,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86287061</t>
+          <t>https://artportalen.se/Sighting/86286594</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>86287062</v>
+        <v>86287061</v>
       </c>
       <c r="B233" t="n">
         <v>80398</v>
@@ -25034,10 +25049,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>394387</v>
+        <v>394475</v>
       </c>
       <c r="R233" t="n">
-        <v>6951722</v>
+        <v>6951692</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>
@@ -25095,13 +25110,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86287062</t>
+          <t>https://artportalen.se/Sighting/86287061</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>86288524</v>
+        <v>86287062</v>
       </c>
       <c r="B234" t="n">
         <v>80398</v>
@@ -25130,22 +25145,19 @@
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Ruvallen Ö, Hjd</t>
+          <t>Ruvallen, Hjd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>394364</v>
+        <v>394387</v>
       </c>
       <c r="R234" t="n">
-        <v>6951769</v>
+        <v>6951722</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -25189,24 +25201,24 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander, Richard Vestin, Nicklas Johansson</t>
+          <t>Julian Klein, Bjarne Tutturen, Barbara Kühn</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86288524</t>
+          <t>https://artportalen.se/Sighting/86287062</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>86288720</v>
+        <v>86288524</v>
       </c>
       <c r="B235" t="n">
         <v>80398</v>
@@ -25244,10 +25256,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>394394</v>
+        <v>394364</v>
       </c>
       <c r="R235" t="n">
-        <v>6951763</v>
+        <v>6951769</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25282,11 +25294,6 @@
           <t>2020-06-15</t>
         </is>
       </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Sälglåga 70-80 cm</t>
-        </is>
-      </c>
       <c r="AD235" t="b">
         <v>0</v>
       </c>
@@ -25310,13 +25317,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86288720</t>
+          <t>https://artportalen.se/Sighting/86288524</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>86375218</v>
+        <v>86288720</v>
       </c>
       <c r="B236" t="n">
         <v>80398</v>
@@ -25345,16 +25352,19 @@
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Ruvallen öst, Hjd</t>
+          <t>Ruvallen Ö, Hjd</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>395147</v>
+        <v>394394</v>
       </c>
       <c r="R236" t="n">
-        <v>6951866</v>
+        <v>6951763</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25389,6 +25399,11 @@
           <t>2020-06-15</t>
         </is>
       </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Sälglåga 70-80 cm</t>
+        </is>
+      </c>
       <c r="AD236" t="b">
         <v>0</v>
       </c>
@@ -25401,24 +25416,24 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Barbara Kühn, Julian Klein, Håkan Thenander, Bo karlstens, Niklas Johansson, Richard Vestin</t>
+          <t>Bo karlstens, Håkan Thenander, Richard Vestin, Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86375218</t>
+          <t>https://artportalen.se/Sighting/86288720</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>86386158</v>
+        <v>86375218</v>
       </c>
       <c r="B237" t="n">
         <v>80398</v>
@@ -25447,19 +25462,16 @@
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Ruvallen Öst, Hjd</t>
+          <t>Ruvallen öst, Hjd</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>395151</v>
+        <v>395147</v>
       </c>
       <c r="R237" t="n">
-        <v>6951745</v>
+        <v>6951866</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25500,7 +25512,6 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
@@ -25512,11 +25523,117 @@
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Richard Vestin, Niklas Johansson, Bo karlstens, Håkan Thenander, Barbara Kühn, Julian Klein</t>
+          <t>Bjarne Tutturen, Barbara Kühn, Julian Klein, Håkan Thenander, Bo karlstens, Niklas Johansson, Richard Vestin</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375218</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>86386158</v>
+      </c>
+      <c r="B238" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Ruvallen Öst, Hjd</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>395151</v>
+      </c>
+      <c r="R238" t="n">
+        <v>6951745</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF238" t="inlineStr"/>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Richard Vestin, Niklas Johansson, Bo karlstens, Håkan Thenander, Barbara Kühn, Julian Klein</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86386158</t>
         </is>
@@ -25760,6 +25877,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110163</v>
+        <v>110168</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110168</v>
+        <v>110171</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110171</v>
+        <v>110177</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110177</v>
+        <v>110178</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110178</v>
+        <v>110190</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110190</v>
+        <v>110191</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>

--- a/artfynd/A 52368-2025 artfynd.xlsx
+++ b/artfynd/A 52368-2025 artfynd.xlsx
@@ -23387,7 +23387,7 @@
         <v>136920799</v>
       </c>
       <c r="B218" t="n">
-        <v>110191</v>
+        <v>110194</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
